--- a/test_automation/Assignment 1 - Test cases.xlsx
+++ b/test_automation/Assignment 1 - Test cases.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\Option 1\Test_automation_Option 1\Test_automation_Option 1\test_automation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kalha\OneDrive\Desktop\SLIIT\3year 1sem\ITPM\ITPM_Assignment1_Option1\test_automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02121B89-E3DB-4032-8CF4-2C2976BCAEB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADD93A1E-2ABA-473A-BDBA-D7AB82D3CF08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="722" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name=" Test cases" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="276">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -38,13 +38,823 @@
   </si>
   <si>
     <t>Status</t>
+  </si>
+  <si>
+    <t>Neg_0001</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>oya monawada karanne</t>
+  </si>
+  <si>
+    <t>ඔයා මොනවාද කරන්නේ</t>
+  </si>
+  <si>
+    <t>ඔයා මොනවද කරන්නෙ</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>Neg_0002</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>api kavuru kiyanako ape group eke leader?</t>
+  </si>
+  <si>
+    <t>අපි කවුරු කියනාකෝ අපේ group එකේ leader?</t>
+  </si>
+  <si>
+    <t>අපි කවුරු කියනකො අපේ group එකේ leader?</t>
+  </si>
+  <si>
+    <t>Neg_0003</t>
+  </si>
+  <si>
+    <t>eka denna bung.</t>
+  </si>
+  <si>
+    <t>එක දෙන්න බං.</t>
+  </si>
+  <si>
+    <t>ඒක දෙන්නා බුන්ග්.</t>
+  </si>
+  <si>
+    <t>Neg_0004</t>
+  </si>
+  <si>
+    <t>api yanawa kiyala kiyanako phone eka switch off karan.</t>
+  </si>
+  <si>
+    <t>අපි යනවා කියලා කියනාකෝ phone එක switch off කරන්.</t>
+  </si>
+  <si>
+    <t>අපි යනවා කියලා කියනකෝ phone එක switch off කරන්.</t>
+  </si>
+  <si>
+    <t>Neg_0005</t>
+  </si>
+  <si>
+    <t>kohomada machan, oyata hondatama innawada?</t>
+  </si>
+  <si>
+    <t>කොහොමද මචං, ඔයාට හොඳටම ඉන්නවද?</t>
+  </si>
+  <si>
+    <t>Neg_0006</t>
+  </si>
+  <si>
+    <t>Subha Upandina machan!</t>
+  </si>
+  <si>
+    <t>සුභ උපන්දිනය මචං!</t>
+  </si>
+  <si>
+    <t>සුභ උපන්දින මචන්!</t>
+  </si>
+  <si>
+    <t>Neg_0007</t>
+  </si>
+  <si>
+    <t>poddak thama inna, mama dannam ennam.</t>
+  </si>
+  <si>
+    <t>පොඩ්ඩක් තාම ඉන්න, මම දැන්නම් එන්නම්.</t>
+  </si>
+  <si>
+    <t>පොඩ්ඩක් තමා ඉන්න, මම දාන්නම් එන්නම්.</t>
+  </si>
+  <si>
+    <t>Neg_0008</t>
+  </si>
+  <si>
+    <t>karunakara me document eka print karala mata denna.</t>
+  </si>
+  <si>
+    <t>කරුණාකර මේ document එක print කරලා මට දෙන්න.</t>
+  </si>
+  <si>
+    <t>Neg_0009</t>
+  </si>
+  <si>
+    <t>nodanna, mata therenne ne.</t>
+  </si>
+  <si>
+    <t>නොදන්නා, මට තේරෙන්නේ නෑ.</t>
+  </si>
+  <si>
+    <t>නොදන්න, මට තේරෙන්නෙ නෑ.</t>
+  </si>
+  <si>
+    <t>Neg_0010</t>
+  </si>
+  <si>
+    <t>aney machan, eka thamai wenne kiyala mata hithune ne.</t>
+  </si>
+  <si>
+    <t>අනේ මචං, ඒක තමයි වෙන්නේ කියලා මට හිතුනේ නෑ.</t>
+  </si>
+  <si>
+    <t>Neg_0011</t>
+  </si>
+  <si>
+    <t>poddak poddak kanna, nathnam stomach eka kiyayi.</t>
+  </si>
+  <si>
+    <t>පොඩ්ඩක් පොඩ්ඩක් කන්න, නැත්නම් stomach එක කියායි.</t>
+  </si>
+  <si>
+    <t>පොඩ්ඩක් පොඩ්ඩක් කන්න, නැත්නම් ස්ටොමච් එක කියයි.</t>
+  </si>
+  <si>
+    <t>Neg_0012</t>
+  </si>
+  <si>
+    <t>ahe ahe yanna, kalin yanna.</t>
+  </si>
+  <si>
+    <t>අහේ අහේ යන්න, කලින් යන්න.</t>
+  </si>
+  <si>
+    <t>Neg_0013</t>
+  </si>
+  <si>
+    <t>mama enna hadanne… api eyata kiyamu neda??</t>
+  </si>
+  <si>
+    <t>මම එන්න හදන්නේ… අපි එයාට කියමු නෙද??</t>
+  </si>
+  <si>
+    <t>මම එන්න හදන්නේ... අපි එයාට කියමු නේද??</t>
+  </si>
+  <si>
+    <t>Neg_0014</t>
+  </si>
+  <si>
+    <t>ane! api hema dawasama late!</t>
+  </si>
+  <si>
+    <t>අනේ! අපි හේම දවසම ලේට්!</t>
+  </si>
+  <si>
+    <t>අනේ! අපි හැම දවසම late!</t>
+  </si>
+  <si>
+    <t>Neg_0015</t>
+  </si>
+  <si>
+    <t>machn oyage phone nmber ek dnnn.</t>
+  </si>
+  <si>
+    <t>මචං ඔයාගේ phone number එක දෙන්නෙ.</t>
+  </si>
+  <si>
+    <t>මචන් ඔයාගේ phone number එක දාන්න.</t>
+  </si>
+  <si>
+    <t>Neg_0016</t>
+  </si>
+  <si>
+    <t>kohomda oya, lassana娘. Dhnwda me message?</t>
+  </si>
+  <si>
+    <t>කොහොමද ඔය, ලස්සන. දන්නවද මේ message?</t>
+  </si>
+  <si>
+    <t>කොහොමද ඔයා, ලස්සන දුවි. දන්නවද මේ message?</t>
+  </si>
+  <si>
+    <t>Neg_0017</t>
+  </si>
+  <si>
+    <t>api heta trip ekak plan karanawa beach ekakata.</t>
+  </si>
+  <si>
+    <t>අපි හෙට trip එකක් plan කරනවා beach එකට.</t>
+  </si>
+  <si>
+    <t>අපි හෙට trip එකක් plan කරනවා beach එකකට.</t>
+  </si>
+  <si>
+    <t>Neg_0018</t>
+  </si>
+  <si>
+    <t>mama office eke project eka finish karapu nisaa bonus ekak libunaa.</t>
+  </si>
+  <si>
+    <t>මම office එකේ project එක finish කරපු නිසා bonus එකක් ලිබුනා.</t>
+  </si>
+  <si>
+    <t>මම office එකේ project එක finish කරපු නිසා bonus එකක් ලැබුණා.</t>
+  </si>
+  <si>
+    <t>Neg_0019</t>
+  </si>
+  <si>
+    <t>mama hithanne oya just wasting time karan inne kiyala.</t>
+  </si>
+  <si>
+    <t>මම හිතන්නේ ඔයා just wasting time කරන් ඉන්නේ කියලා.</t>
+  </si>
+  <si>
+    <t>Neg_0020</t>
+  </si>
+  <si>
+    <t>api get together ekak hadamu this weekend.</t>
+  </si>
+  <si>
+    <t>අපි get together එකක් හදාමු this weekend.</t>
+  </si>
+  <si>
+    <t>අපි get together එකක් හදමු this weekend.</t>
+  </si>
+  <si>
+    <t>Neg_0021</t>
+  </si>
+  <si>
+    <t>oyage laptop eke RAM kochcharada thiyenne?</t>
+  </si>
+  <si>
+    <t>ඔයාගේ laptop එකේ RAM කොච්චරද තියෙන්නේ?</t>
+  </si>
+  <si>
+    <t>ඔයාගෙ laptop එකේ RAM කොච්චරද තියෙන්නේ?</t>
+  </si>
+  <si>
+    <t>Neg_0022</t>
+  </si>
+  <si>
+    <t>me software eka update karada? Bluetooth eka connect wenawada?</t>
+  </si>
+  <si>
+    <t>මේ software එක update කරද? Bluetooth එක connect වෙනවද?</t>
+  </si>
+  <si>
+    <t>මේ software එක update කරාද? Bluetooth එක connect වෙනවාද?</t>
+  </si>
+  <si>
+    <t>Neg_0023</t>
+  </si>
+  <si>
+    <t>mama Instagram eke story ekak dammaa, oya dakkeda?</t>
+  </si>
+  <si>
+    <t>මම Instagram එකේ story එකක් දම්මා, ඔයා දැක්කද?</t>
+  </si>
+  <si>
+    <t>මම Instagram එකේ story එකක් දැම්මා, ඔයා දැක්කෙද?</t>
+  </si>
+  <si>
+    <t>Neg_0024</t>
+  </si>
+  <si>
+    <t>Tiktok eke viral wechcha video eka oya dakkeda?</t>
+  </si>
+  <si>
+    <t>Tiktok එකේ viral වෙච්ච video එක ඔයා දැක්කද?</t>
+  </si>
+  <si>
+    <t>Tiktok එකේ viral වෙච්ච video එක ඔයා දැක්කේද?</t>
+  </si>
+  <si>
+    <t>Neg_0025</t>
+  </si>
+  <si>
+    <t>API eka fix wenawada kiyala QA team eka check karanawa.</t>
+  </si>
+  <si>
+    <t>API එක fix වෙනවද කියලා QA team එක check කරනවා.</t>
+  </si>
+  <si>
+    <t>API ඒක fix වෙනවද කියලා QA team එක check කරනවා.</t>
+  </si>
+  <si>
+    <t>Neg_0026</t>
+  </si>
+  <si>
+    <t>RSVP karanna beri wunaa, GPS eka off wela thibbaa.</t>
+  </si>
+  <si>
+    <t>RSVP කරන්න බෑරි වුනා, GPS එක off වෙලා තිබ්බා.</t>
+  </si>
+  <si>
+    <t>RSVP කරන්න බැරි වුණා, GPS ඒක off වෙලා තිබ්බා.</t>
+  </si>
+  <si>
+    <t>Neg_0027</t>
+  </si>
+  <si>
+    <t>heta uni eke pres eka thiyanawa, oya enawada?</t>
+  </si>
+  <si>
+    <t>හෙට uni එකේ pres එක තියනවා, ඔයා එනවද?</t>
+  </si>
+  <si>
+    <t>හෙට uni එකේ ප්රෙස් එක තියනවා, ඔයා එනවද?</t>
+  </si>
+  <si>
+    <t>Neg_0028</t>
+  </si>
+  <si>
+    <t>doc eka ready karala sub karannam heta.</t>
+  </si>
+  <si>
+    <t>doc එක ready කරලා sub කරන්නම් හෙට.</t>
+  </si>
+  <si>
+    <t>Neg_0029</t>
+  </si>
+  <si>
+    <t>api Colombo 3 walata yanawa, Galle Face eke hitamu.</t>
+  </si>
+  <si>
+    <t>අපි Colombo 3 වලට යනවා, Galle Face එකේ හිටාමු.</t>
+  </si>
+  <si>
+    <t>අපි Colombo 3 වලට යනවා, Galle Face එකේ හිටමු.</t>
+  </si>
+  <si>
+    <t>Neg_0030</t>
+  </si>
+  <si>
+    <t>Kandy Peradeniya diga drive ekak yamuda?</t>
+  </si>
+  <si>
+    <t>Kandy Peradeniya දිගා drive එකක් යමුද?</t>
+  </si>
+  <si>
+    <t>Kandy Peradeniya දිග drive එකක් යමුද?</t>
+  </si>
+  <si>
+    <t>Neg_0031</t>
+  </si>
+  <si>
+    <t>Tharindi akka enna kiwwada, api yamu dennama?</t>
+  </si>
+  <si>
+    <t>Tharindi අක්කා එන්න කිව්වද, අපි යමු දෙන්නම?</t>
+  </si>
+  <si>
+    <t>තරිඳි අක්කා එන්න කිව්වද, අපි යමු දෙන්නම?</t>
+  </si>
+  <si>
+    <t>Neg_0032</t>
+  </si>
+  <si>
+    <t>Nimal aiya saha Kamani akka wedding eka next month.</t>
+  </si>
+  <si>
+    <t>Nimal අයියා සහ Kamani අක්කා wedding එක next month.</t>
+  </si>
+  <si>
+    <t>නිමල් අයියා සහ කමනි අක්කා wedding එක next month.</t>
+  </si>
+  <si>
+    <t>Neg_0033</t>
+  </si>
+  <si>
+    <t>mama 2nd year eke, 3rd semester eka hadagannawa.</t>
+  </si>
+  <si>
+    <t>මම 2nd year එකේ, 3rd semester එක හදාගන්නවා.</t>
+  </si>
+  <si>
+    <t>Neg_0034</t>
+  </si>
+  <si>
+    <t>me bus eka 10min witharada late wenne? 15minnak giye.</t>
+  </si>
+  <si>
+    <t>මේ bus එක 10min විතරද late වෙන්නේ? 15minnak ගියේ.</t>
+  </si>
+  <si>
+    <t>මේ bus එක 10min විතරද late වෙන්නේ? 15මින්නක් ගියේ.</t>
+  </si>
+  <si>
+    <t>Neg_0035</t>
+  </si>
+  <si>
+    <t>me jacket eka LKR 4500 ta gatta, salli wadi neda?</t>
+  </si>
+  <si>
+    <t>මේ jacket එක LKR 4500 ට ගත්තා, සල්ලි වාඩී නෙද?</t>
+  </si>
+  <si>
+    <t>මේ ජැකට් එක LKR 4500 ට ගත්තා, සල්ලි වැඩි නේද?</t>
+  </si>
+  <si>
+    <t>Neg_0036</t>
+  </si>
+  <si>
+    <t>USD 50 la exchange rate eka kohomada ada?</t>
+  </si>
+  <si>
+    <t>USD 50 ල exchange rate එක කොහොමද අද?</t>
+  </si>
+  <si>
+    <t>USD 50 ලා exchange rate එක කොහොමද අද?</t>
+  </si>
+  <si>
+    <t>Neg_0037</t>
+  </si>
+  <si>
+    <t>api 8:00AM ta hadaganna one, ela bae.</t>
+  </si>
+  <si>
+    <t>අපි 8:00AM ට හදාගන්න ඕනේ, ඒල බෑ.</t>
+  </si>
+  <si>
+    <t>අපි 8:00AM ට හදාගන්න ඕනේ, එල බෑ.</t>
+  </si>
+  <si>
+    <t>Neg_0038</t>
+  </si>
+  <si>
+    <t>class eka 2:30pm ta pawel, 4:00pm ta nimbei.</t>
+  </si>
+  <si>
+    <t>class එක 2:30pm ට පාවෙල්, 4:00pm ට නිමෙයි.</t>
+  </si>
+  <si>
+    <t>Neg_0039</t>
+  </si>
+  <si>
+    <t>deadline eka April 30 ta, heta 29 ne ada.</t>
+  </si>
+  <si>
+    <t>deadline එක April 30 ට, හෙට 29 නෙ අද.</t>
+  </si>
+  <si>
+    <t>deadline එක April 30 ට, හෙට 29 නෑ අද.</t>
+  </si>
+  <si>
+    <t>Neg_0040</t>
+  </si>
+  <si>
+    <t>2025-12-25 Christmas day, ape holiday confirm.</t>
+  </si>
+  <si>
+    <t>2025-12-25 Christmas day, අපේ holiday confirm.</t>
+  </si>
+  <si>
+    <t>Neg_0041</t>
+  </si>
+  <si>
+    <t>me bag eka 5kg withara dana, bahawenna amaru.</t>
+  </si>
+  <si>
+    <t>මේ bag එක 5kg විතර දාන, බාහවෙන්න අමාරු.</t>
+  </si>
+  <si>
+    <t>මේ බෑග් එක 5kg විතර දාන, බහවෙන්න අමාරු.</t>
+  </si>
+  <si>
+    <t>Neg_0042</t>
+  </si>
+  <si>
+    <t>me road eka 200m withara wela innawa, bus stop eka.</t>
+  </si>
+  <si>
+    <t>මේ road එක 200m විතර වෙලා ඉන්නවා, bus stop එක.</t>
+  </si>
+  <si>
+    <t>Neg_0043</t>
+  </si>
+  <si>
+    <t>Meka mara fire da? Chee yako, balanna bae.</t>
+  </si>
+  <si>
+    <t>මේකා මාර fire ද? චී යකෝ, බලන්න බෑ.</t>
+  </si>
+  <si>
+    <t>මේක මාර fire ද? චී යකෝ, බලන්න බෑ.</t>
+  </si>
+  <si>
+    <t>Neg_0044</t>
+  </si>
+  <si>
+    <t>aney da, uba athe kanna giya wede neda?</t>
+  </si>
+  <si>
+    <t>අනේ ද, උඹ අතේ කන්න ගිය වැඩේ නෙද?</t>
+  </si>
+  <si>
+    <t>Neg_0045</t>
+  </si>
+  <si>
+    <t>me portfolio eka balanna: https://mysite.dev/portfolio kiyala.</t>
+  </si>
+  <si>
+    <t>මේ portfolio එක බලන්න: https://mysite.dev/portfolio කියලා.</t>
+  </si>
+  <si>
+    <t>Neg_0046</t>
+  </si>
+  <si>
+    <t>mata CV eka email karanna: jobs.apply99@outlook.com</t>
+  </si>
+  <si>
+    <t>මට CV එක email කරන්න: jobs.apply99@outlook.com</t>
+  </si>
+  <si>
+    <t>මට CV ඒක email කරන්න: jobs.apply99@outlook.com</t>
+  </si>
+  <si>
+    <t>Neg_0047</t>
+  </si>
+  <si>
+    <t>mata godak godak santhosai 🎉 api denna hondatama kare.</t>
+  </si>
+  <si>
+    <t>මට ගොඩක් ගොඩක් සන්තෝසයි 🎉 අපි දෙන්නා හොඳටම කාරේ.</t>
+  </si>
+  <si>
+    <t>මට ගොඩක් ගොඩක් සන්තෝසයි 🎉 අපි දෙන්න හොඳටම කරේ.</t>
+  </si>
+  <si>
+    <t>Neg_0048</t>
+  </si>
+  <si>
+    <t>boru kiyanne epa 🤥 api dannawa.</t>
+  </si>
+  <si>
+    <t>බොරු කියන්නේ එපා 🤥 අපි දන්නවා.</t>
+  </si>
+  <si>
+    <t>බොරු කියන්නෙ එපා 🤥 අපි දන්නවා.</t>
+  </si>
+  <si>
+    <t>Neg_0049</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>machan api heta 9:30AM ta Colombo train eken yanawa. Train eka Rs. 350 ne. Tharidu akka saha Nimal aiya dennama enavalu. Group eke hemoma WhatsApp eken confirm karanna. RSVP karanna beri wuna kiyanna epa, 29th ta last date. poddak poddak kanna, trip eke bahawenawa.</t>
+  </si>
+  <si>
+    <t>මචං අපි හෙට 9:30AM ට Colombo train එකෙන් යනවා. Train එක Rs. 350 නෙ. Tharidu අක්කා සහ Nimal අයියා දෙන්නම එනවාලු. Group එකේ හේමෝම WhatsApp එකෙන් confirm කරන්න. RSVP කරන්න බෑරි වුනා කියන්න එපා, 29th ට last date. පොඩ්ඩක් පොඩ්ඩක් කන්න, trip එකේ බාහෙනවා.</t>
+  </si>
+  <si>
+    <t>මචං අපි හෙට 9:30ට Colombo train එකෙන් යනවා. Train එක Rs. 350 නෑ. තරිදු අක්කා සහ නිමල් අයියා දෙන්නම එනවලු. Group එකේ හැමෝම WhatsApp ඒකෙන් confirm කරන්න. RSVP කරන්න බැරි වුණා කියන්න එපා, 29ත් ට last date. පොඩ්ඩක් පොඩ්ඩක් කන්න, trip එකේ බහිනවා.</t>
+  </si>
+  <si>
+    <t>Neg_0050</t>
+  </si>
+  <si>
+    <t>aney bro 😅 meka mara situation ekak. API eka crash wela, boss ASAP fix karanna kiwwa. Mama 2:00PM ta meeting ekak thiyanawa, eka miss karannam bae. Tharuka saha Dulaj dennama office ekkata awe 8:00AM ta. me bug eka 500 lines withara code eke thiyanawa. laptop eke RAM 8GB, it's not enough for this. api heta September 15 wenakan fix karanna hadanawa.</t>
+  </si>
+  <si>
+    <t>අනේ bro 😅 මේකා මාර situation එකක්. API එක crash වෙලා, boss ASAP fix කරන්න කිව්වා. මම 2:00PM ට meeting එකක් තියනවා, ඒක miss කරන්නම් බෑ. Tharuka සහ Dulaj දෙන්නම office එකට ආවේ 8:00AM ට. මේ bug එක 500 lines විතර code එකේ තියනවා. laptop එකේ RAM 8GB, it's not enough for this. අපි හෙට September 15 වෙනකන් fix කරන්න හදනවා.</t>
+  </si>
+  <si>
+    <t>අනේ bro 😅 මේක මාර situation එකක්. API ඒක crash වෙලා, boss ASAP fix කරන්න කිව්වා. මම 2:00PM ට meeting එකක් තියෙනවා, ඒක miss කරන්නම් බෑ. තරුක සහ දුලාජ් දෙන්නම office එක්කට ආවේ 8:00AM ට. මේ bug එක 500 ලයින්ස් විතර කෝඩ් එකේ තියෙනවා. laptop එකේ RAM 8GB, it's not enough for this. අපි හෙට September 15 වෙනකන් fix කරන්න හදනවා.</t>
+  </si>
+  <si>
+    <t>Singlish input types covered</t>
+  </si>
+  <si>
+    <t>Evidence or rationale for the input type covered</t>
+  </si>
+  <si>
+    <t>Question forms</t>
+  </si>
+  <si>
+    <t>Rationale: The sentence is structured as a question with 'koheda' (where) indicating interrogative form</t>
+  </si>
+  <si>
+    <t>Rationale: 'kiyanako' is an informal question tag meaning 'who do you say/think'; overall sentence is a question</t>
+  </si>
+  <si>
+    <t>Command forms</t>
+  </si>
+  <si>
+    <t>Rationale: 'denna' is a command (give it); 'bung' is a colloquial Sinhala particle</t>
+  </si>
+  <si>
+    <t>Rationale: 'karan' at the end gives a command/imperative meaning; the sentence is an instruction</t>
+  </si>
+  <si>
+    <t>Greetings</t>
+  </si>
+  <si>
+    <t>Rationale: 'kohomada machan' is a casual greeting meaning 'how are you buddy'</t>
+  </si>
+  <si>
+    <t>Rationale: 'Subha Upandina' is a common Singlish birthday greeting</t>
+  </si>
+  <si>
+    <t>Requests</t>
+  </si>
+  <si>
+    <t>Rationale: 'poddak thama inna' is a polite request to wait a little longer</t>
+  </si>
+  <si>
+    <t>Rationale: 'karunakara … denna' is a polite request form; contains English noun 'document' and 'print'</t>
+  </si>
+  <si>
+    <t>Responses</t>
+  </si>
+  <si>
+    <t>Rationale: 'nodanna, mata therenne ne' is a common response meaning 'I don't know, I don't understand'</t>
+  </si>
+  <si>
+    <t>Rationale: The sentence is a reactive response expressing surprise; uses colloquial particles 'thamai' and 'ne'</t>
+  </si>
+  <si>
+    <t>Repeated Words</t>
+  </si>
+  <si>
+    <t>Rationale: 'poddak poddak' is a repeated word pattern meaning 'eat little by little'</t>
+  </si>
+  <si>
+    <t>Rationale: 'ahe ahe' is a colloquial repeated exclamation urging someone to go quickly</t>
+  </si>
+  <si>
+    <t>Inputs with Punctuation Marks</t>
+  </si>
+  <si>
+    <t>Evidence: Uses '…' (ellipsis) and '??' (double question marks) as punctuation within the sentence</t>
+  </si>
+  <si>
+    <t>Evidence: Contains '!' punctuation marks at two positions in the sentence</t>
+  </si>
+  <si>
+    <t>Romanization / Spelling Variants</t>
+  </si>
+  <si>
+    <t>Rationale: Words like 'machn' (machan), 'nmber' (number), 'dnnn' (denna) are heavily truncated spelling variants</t>
+  </si>
+  <si>
+    <t>Rationale: 'kohomda' and 'Dhnwda' are shortened spelling variants of 'kohomada' and 'dannawada'</t>
+  </si>
+  <si>
+    <t>Isolated English Word Insertions in Singlish</t>
+  </si>
+  <si>
+    <t>Rationale: 'trip', 'plan', 'beach' are single English words inserted within Singlish text</t>
+  </si>
+  <si>
+    <t>Rationale: 'project', 'finish', 'bonus' are isolated English words inserted in Singlish sentence</t>
+  </si>
+  <si>
+    <t>Multi-Word English Phrases in Singlish</t>
+  </si>
+  <si>
+    <t>Rationale: 'just wasting time' is a multi-word English phrase embedded in a Singlish sentence</t>
+  </si>
+  <si>
+    <t>Rationale: 'get together' and 'this weekend' are consecutive English words forming phrases inside Singlish</t>
+  </si>
+  <si>
+    <t>English Digital Terms in Singlish</t>
+  </si>
+  <si>
+    <t>Rationale: 'laptop' and 'RAM' are digital technology terms inserted in Singlish</t>
+  </si>
+  <si>
+    <t>Rationale: 'software', 'update', 'Bluetooth', 'connect' are digital terms embedded in Singlish</t>
+  </si>
+  <si>
+    <t>Platform/App Names in Singlish</t>
+  </si>
+  <si>
+    <t>Rationale: 'Instagram' is a platform name and 'story' is an app-specific feature name embedded in Singlish</t>
+  </si>
+  <si>
+    <t>Rationale: 'Tiktok' is a platform name; 'viral wechcha video eka' is colloquial Singlish around it</t>
+  </si>
+  <si>
+    <t>English Abbreviations/Acronyms in Singlish</t>
+  </si>
+  <si>
+    <t>Rationale: 'API' and 'QA' are technical acronyms embedded in a Singlish sentence</t>
+  </si>
+  <si>
+    <t>Rationale: 'RSVP' is an abbreviation and 'GPS' is an acronym; both are embedded in Singlish</t>
+  </si>
+  <si>
+    <t>English Clipped Forms in Singlish</t>
+  </si>
+  <si>
+    <t>Rationale: 'uni' is a clipped form of 'university' and 'pres' is a clipped form of 'presentation'</t>
+  </si>
+  <si>
+    <t>Rationale: 'doc' is a clipped form of 'document' and 'sub' is a clipped form of 'submit'</t>
+  </si>
+  <si>
+    <t>Place Names Embedded in Singlish</t>
+  </si>
+  <si>
+    <t>Rationale: 'Colombo 3' and 'Galle Face' are proper place names embedded in Singlish</t>
+  </si>
+  <si>
+    <t>Rationale: 'Kandy' and 'Peradeniya' are Sri Lankan place names embedded in Singlish</t>
+  </si>
+  <si>
+    <t>Person Names Embedded in Singlish</t>
+  </si>
+  <si>
+    <t>Rationale: 'Tharindi akka' embeds a female name 'Tharindi' with the Sinhala kin term 'akka'</t>
+  </si>
+  <si>
+    <t>Rationale: 'Nimal' and 'Kamani' are person names; 'aiya' and 'akka' are Sinhala kin terms mixed with English words</t>
+  </si>
+  <si>
+    <t>Inputs with Numbers and Numeric Suffixes</t>
+  </si>
+  <si>
+    <t>Rationale: '2nd' and '3rd' are ordinal numeric suffixes embedded in a Singlish sentence</t>
+  </si>
+  <si>
+    <t>Rationale: '10min' and '15minnak' are numbers with unit suffixes used in informal chat</t>
+  </si>
+  <si>
+    <t>Inputs with Currency</t>
+  </si>
+  <si>
+    <t>Rationale: 'LKR 4500' is a currency notation embedded in a Singlish sentence</t>
+  </si>
+  <si>
+    <t>Rationale: 'USD 50' is a currency value; 'exchange rate' is an English term embedded in Singlish</t>
+  </si>
+  <si>
+    <t>Inputs with Time Formats</t>
+  </si>
+  <si>
+    <t>Rationale: '8:00AM' is a time format with AM suffix embedded in Singlish</t>
+  </si>
+  <si>
+    <t>Rationale: Contains two time formats '2:30pm' and '4:00pm' within the same Singlish input</t>
+  </si>
+  <si>
+    <t>Inputs with Dates</t>
+  </si>
+  <si>
+    <t>Rationale: 'April 30' is a date expression with English month name embedded in Singlish</t>
+  </si>
+  <si>
+    <t>Rationale: '2025-12-25' is an ISO-format date and 'Christmas day' is an English phrase inside Singlish</t>
+  </si>
+  <si>
+    <t>Inputs with Unit of Measurements</t>
+  </si>
+  <si>
+    <t>Rationale: '5kg' is a weight measurement unit embedded in a Singlish sentence</t>
+  </si>
+  <si>
+    <t>Rationale: '200m' is a distance measurement; 'bus stop' is an English compound noun embedded in Singlish</t>
+  </si>
+  <si>
+    <t>Inputs with Slang and Casual Phrasing</t>
+  </si>
+  <si>
+    <t>Rationale: 'mara fire' is slang for 'extremely impressive'; 'Chee yako' is a casual/slang exclamation</t>
+  </si>
+  <si>
+    <t>Rationale: 'uba athe kanna giya wede neda' is a Sinhala idiomatic/slang phrase meaning 'didn't that backfire on you'</t>
+  </si>
+  <si>
+    <t>Online Identifiers in Singlish</t>
+  </si>
+  <si>
+    <t>Evidence: Contains a full URL 'https://mysite.dev/portfolio' embedded in a Singlish sentence</t>
+  </si>
+  <si>
+    <t>Evidence: Contains an email address 'jobs.apply99@outlook.com' embedded within Singlish text</t>
+  </si>
+  <si>
+    <t>Inputs Containing Emojis</t>
+  </si>
+  <si>
+    <t>Evidence: Contains emoji 🎉 embedded between Singlish words; emoji must be preserved in output</t>
+  </si>
+  <si>
+    <t>Evidence: Contains emoji 🤥 (lying face) as part of a warning statement in Singlish</t>
+  </si>
+  <si>
+    <t>Question forms; Requests; Repeated Words; Inputs with Punctuation Marks; Romanization / Spelling Variants; Isolated English Word Insertions in Singlish; Platform/App Names in Singlish; English Abbreviations/Acronyms in Singlish; Place Names Embedded in Singlish; Person Names Embedded in Singlish; Inputs with Numbers and Numeric Suffixes; Inputs with Currency; Inputs with Time Formats</t>
+  </si>
+  <si>
+    <t>Evidence: '9:30AM' (time format); 'Rs. 350' (currency); 'Tharidu akka / Nimal aiya' (person names + kin terms); 'WhatsApp' (platform name); 'RSVP' (abbreviation); '29th' (numeric ordinal suffix); 'poddak poddak' (repeated word). Rationale: Long complex message covering many Singlish input types simultaneously.</t>
+  </si>
+  <si>
+    <t>Inputs Containing Emojis; English Abbreviations/Acronyms in Singlish; Person Names Embedded in Singlish; Inputs with Numbers and Numeric Suffixes; Inputs with Time Formats; Inputs with Dates; English Digital Terms in Singlish; Multi-Word English Phrases in Singlish; Inputs with Slang and Casual Phrasing</t>
+  </si>
+  <si>
+    <t>Evidence: '😅' (emoji); 'API', 'ASAP' (acronyms); '2:00PM', '8:00AM' (time formats); 'Tharuka', 'Dulaj' (person names); '500 lines', '8GB' (numbers+units); 'September 15' (date); 'it's not enough for this' (multi-word English phrase); 'mara situation' (slang)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -53,8 +863,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
-      <sz val="8.5"/>
+      <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -72,21 +888,39 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Iskoola Pota"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -111,25 +945,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FFB0B0B0"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FFB0B0B0"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
+      <top style="thin">
+        <color rgb="FFB0B0B0"/>
+      </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FFB0B0B0"/>
       </bottom>
       <diagonal/>
     </border>
@@ -137,34 +962,53 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -211,20 +1055,20 @@
         <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -254,12 +1098,12 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -298,258 +1142,1514 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:tint val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="9500"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:tint val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="49.95" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="A1:H51"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" customWidth="1"/>
-    <col min="3" max="3" width="22.109375" customWidth="1"/>
-    <col min="4" max="4" width="25.33203125" customWidth="1"/>
-    <col min="5" max="5" width="22.5546875" customWidth="1"/>
-    <col min="7" max="7" width="14.33203125" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="10" width="12.33203125" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.21875" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="44.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="56.77734375" style="9" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="50.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="93.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="8.88671875" style="5" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" s="3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="7"/>
-    </row>
-    <row r="3" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-    </row>
-    <row r="4" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-    </row>
-    <row r="6" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
+      <c r="G1" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" s="3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" s="3" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="H22" s="12" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="H23" s="12" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="H24" s="12" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="H25" s="12" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="H26" s="12" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="H27" s="12" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="H28" s="12" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="H29" s="12" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G30" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="H30" s="12" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G31" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="H31" s="12" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G32" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="H32" s="12" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G33" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="H33" s="12" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G34" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="H34" s="12" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G35" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="H35" s="12" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G36" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="H36" s="12" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="H37" s="12" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G38" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="H38" s="12" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G39" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="H39" s="12" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G40" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="H40" s="12" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G41" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="H41" s="12" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G42" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="H42" s="12" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G43" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="H43" s="12" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G44" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="H44" s="12" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G45" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="H45" s="12" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G46" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="H46" s="12" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G47" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="H47" s="12" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G48" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="H48" s="12" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G49" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="H49" s="12" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="91.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G50" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="H50" s="12" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="122.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G51" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="H51" s="12" t="s">
+        <v>275</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="C2:C5"/>
-    <mergeCell ref="D6:D9"/>
-    <mergeCell ref="F2:F5"/>
-    <mergeCell ref="E2:E5"/>
-    <mergeCell ref="E6:E9"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="F6:F9"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="C6:C9"/>
-    <mergeCell ref="D2:D5"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>